--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -57895,6 +57895,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -57926,18 +57926,41 @@
         <v>20000</v>
       </c>
       <c r="C2503" t="n">
-        <v>0.349999994039536</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="D2503" t="n">
-        <v>0.349999994039536</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="E2503" t="n">
-        <v>0.349999994039536</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="F2503" t="n">
         <v>0.319999992847443</v>
       </c>
       <c r="G2503" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>41522</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2504" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -57955,7 +57955,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="E2504" t="n">
-        <v>0.349999994039536</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="F2504" t="n">
         <v>0.335999995470047</v>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -57964,6 +57964,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -57828,7 +57828,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2499" t="n">
         <v>0</v>
@@ -57851,10 +57851,10 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2500" t="n">
-        <v>355</v>
+        <v>0</v>
       </c>
       <c r="C2500" t="n">
         <v>0.358000010251999</v>
@@ -57874,22 +57874,22 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2501" t="n">
-        <v>1220</v>
+        <v>355</v>
       </c>
       <c r="C2501" t="n">
-        <v>0.349999994039536</v>
+        <v>0.358000010251999</v>
       </c>
       <c r="D2501" t="n">
-        <v>0.349999994039536</v>
+        <v>0.358000010251999</v>
       </c>
       <c r="E2501" t="n">
-        <v>0.349999994039536</v>
+        <v>0.358000010251999</v>
       </c>
       <c r="F2501" t="n">
-        <v>0.349999994039536</v>
+        <v>0.358000010251999</v>
       </c>
       <c r="G2501" t="s">
         <v>7</v>
@@ -57897,10 +57897,10 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2502" t="n">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="C2502" t="n">
         <v>0.349999994039536</v>
@@ -57920,22 +57920,22 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2503" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="C2503" t="n">
-        <v>0.319999992847443</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="D2503" t="n">
-        <v>0.319999992847443</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="E2503" t="n">
-        <v>0.319999992847443</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="F2503" t="n">
-        <v>0.319999992847443</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="G2503" t="s">
         <v>7</v>
@@ -57943,13 +57943,13 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2504" t="n">
-        <v>41522</v>
+        <v>20000</v>
       </c>
       <c r="C2504" t="n">
-        <v>0.335999995470047</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="D2504" t="n">
         <v>0.319999992847443</v>
@@ -57958,7 +57958,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="F2504" t="n">
-        <v>0.335999995470047</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="G2504" t="s">
         <v>7</v>
@@ -57966,24 +57966,47 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2505" t="n">
-        <v>0</v>
+        <v>41522</v>
       </c>
       <c r="C2505" t="n">
         <v>0.335999995470047</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.335999995470047</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.335999995470047</v>
+        <v>0.319999992847443</v>
       </c>
       <c r="F2505" t="n">
         <v>0.335999995470047</v>
       </c>
       <c r="G2505" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2506" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58010,6 +58010,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58056,6 +58056,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58079,6 +58079,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58102,6 +58102,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58125,6 +58125,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58148,6 +58148,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>801</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2514"/>
+      <c r="G2514" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58187,8 +58187,33 @@
       <c r="E2514" t="n">
         <v>0.340000003576279</v>
       </c>
-      <c r="F2514"/>
+      <c r="F2514" t="n">
+        <v>0.340000003576279</v>
+      </c>
       <c r="G2514" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>54603</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.324000000953674</v>
+      </c>
+      <c r="G2515" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58217,6 +58217,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>6466</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>0.303999990224838</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>0.317999988794327</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58240,6 +58240,27 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>140</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="F2517"/>
+      <c r="G2517" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58256,8 +58256,33 @@
       <c r="E2517" t="n">
         <v>0.331999987363815</v>
       </c>
-      <c r="F2517"/>
+      <c r="F2517" t="n">
+        <v>0.331999987363815</v>
+      </c>
       <c r="G2517" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>25162</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>0.316000014543533</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="G2518" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58286,6 +58286,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>740</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="F2520"/>
+      <c r="G2520" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58325,8 +58325,31 @@
       <c r="E2520" t="n">
         <v>0.300000011920929</v>
       </c>
-      <c r="F2520"/>
+      <c r="F2520" t="n">
+        <v>0.330000013113022</v>
+      </c>
       <c r="G2520" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>7838</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>0.328000009059906</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>0.328000009059906</v>
+      </c>
+      <c r="F2521"/>
+      <c r="G2521" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58348,8 +58348,31 @@
       <c r="E2521" t="n">
         <v>0.328000009059906</v>
       </c>
-      <c r="F2521"/>
+      <c r="F2521" t="n">
+        <v>0.300000011920929</v>
+      </c>
       <c r="G2521" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>5125</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>0.303999990224838</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="F2522"/>
+      <c r="G2522" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58371,8 +58371,31 @@
       <c r="E2522" t="n">
         <v>0.28999999165535</v>
       </c>
-      <c r="F2522"/>
+      <c r="F2522" t="n">
+        <v>0.301999986171722</v>
+      </c>
       <c r="G2522" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>0.305999994277954</v>
+      </c>
+      <c r="F2523"/>
+      <c r="G2523" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58394,7 +58394,9 @@
       <c r="E2523" t="n">
         <v>0.305999994277954</v>
       </c>
-      <c r="F2523"/>
+      <c r="F2523" t="n">
+        <v>0.314000010490417</v>
+      </c>
       <c r="G2523" t="s">
         <v>7</v>
       </c>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58401,6 +58401,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>22355</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58424,6 +58424,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>0.303999990224838</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>3814</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>0.28999999165535</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58470,6 +58470,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>1205</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -58493,6 +58493,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73719,6 +73719,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2530">
+      <c r="A2530" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2530" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="G2530" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="H2530" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73748,6 +73748,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2531">
+      <c r="A2531" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2531" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="G2531" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="H2531" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2532" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="G2532" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="H2532" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73806,6 +73806,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2533">
+      <c r="A2533" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2533" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="G2533" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="H2533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73835,6 +73835,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2534">
+      <c r="A2534" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2534" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="G2534" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="H2534" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2535" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>0.287999987602234</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="G2535" t="n">
+        <v>0.259999990463257</v>
+      </c>
+      <c r="H2535" t="n">
+        <v>311</v>
+      </c>
+      <c r="I2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73872,13 +73872,13 @@
         <v>46322.3333333333</v>
       </c>
       <c r="C2535" t="n">
-        <v>0.287999987602234</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="D2535" t="n">
-        <v>0.287999987602234</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="E2535" t="n">
-        <v>0.287999987602234</v>
+        <v>0.259999990463257</v>
       </c>
       <c r="F2535" t="n">
         <v>0.259999990463257</v>
@@ -73890,6 +73890,35 @@
         <v>311</v>
       </c>
       <c r="I2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2536" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>0.257999986410141</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>0.244000002741814</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="G2536" t="n">
+        <v>0.256000012159348</v>
+      </c>
+      <c r="H2536" t="n">
+        <v>33500</v>
+      </c>
+      <c r="I2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73922,6 +73922,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2537">
+      <c r="A2537" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2537" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G2537" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H2537" t="n">
+        <v>54</v>
+      </c>
+      <c r="I2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BWZ.MI.xlsx
+++ b/data/BWZ.MI.xlsx
@@ -73951,6 +73951,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2538">
+      <c r="A2538" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2538" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G2538" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H2538" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
